--- a/results_polyp/Results_1_ClinicDB_test.xlsx
+++ b/results_polyp/Results_1_ClinicDB_test.xlsx
@@ -472,22 +472,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7756</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6334</v>
+        <v>0.9049</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6567</v>
+        <v>0.9436</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9948</v>
+        <v>0.994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.947</v>
+        <v>0.9567</v>
       </c>
       <c r="G2" t="n">
-        <v>26.203</v>
+        <v>4.1231</v>
       </c>
     </row>
     <row r="3">
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9614</v>
+        <v>0.9084</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9257</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9849</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9976</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3852</v>
+        <v>28.6325</v>
       </c>
     </row>
     <row r="4">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9701</v>
+        <v>0.9735</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9483</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9697</v>
+        <v>0.9708</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983</v>
+        <v>0.9986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9706</v>
+        <v>0.9762</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9717</v>
       </c>
       <c r="C5" t="n">
-        <v>0.931</v>
+        <v>0.9449</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9655</v>
+        <v>0.9681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9971</v>
+        <v>0.9981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.963</v>
+        <v>0.9752</v>
       </c>
       <c r="G5" t="n">
-        <v>20.2051</v>
+        <v>4.1649</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9771</v>
+        <v>0.9826</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9552</v>
+        <v>0.9657</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9885</v>
+        <v>0.9827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9921</v>
+        <v>0.996</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9659</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>39.9098</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9539</v>
+        <v>0.9464</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9119</v>
+        <v>0.8982</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9465</v>
+        <v>0.9041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9983</v>
+        <v>0.9997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9615</v>
+        <v>0.9927</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1231</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9597</v>
+        <v>0.9304</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9226</v>
+        <v>0.8698</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.8808</v>
       </c>
       <c r="E8" t="n">
-        <v>0.999</v>
+        <v>0.9998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9447</v>
+        <v>0.9859</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -647,22 +647,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9571</v>
+        <v>0.9621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9177</v>
+        <v>0.927</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9848</v>
+        <v>0.9534</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9976</v>
+        <v>0.9991</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6056</v>
+        <v>2.8284</v>
       </c>
     </row>
     <row r="10">
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9677</v>
+        <v>0.9673</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9375</v>
+        <v>0.9366</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9701</v>
+        <v>0.9567</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9978</v>
+        <v>0.9986</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9653</v>
+        <v>0.9781</v>
       </c>
       <c r="G10" t="n">
         <v>2.8284</v>
@@ -697,22 +697,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9595</v>
+        <v>0.9737</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9222</v>
+        <v>0.9488</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9881</v>
+        <v>0.9648</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9992</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9325</v>
+        <v>0.9828</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="12">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.963</v>
+        <v>0.9363</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9286</v>
+        <v>0.8802</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9545</v>
+        <v>0.8837</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9991</v>
+        <v>0.9999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9716</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6056</v>
+        <v>4.4721</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9536</v>
+        <v>0.9376</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9113</v>
+        <v>0.8825</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9708</v>
+        <v>0.8907</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9896</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0081</v>
+        <v>3.6056</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9604</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9238</v>
+        <v>0.9253</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9403</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9993</v>
+        <v>0.9997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9813</v>
+        <v>0.9912</v>
       </c>
       <c r="G14" t="n">
-        <v>8.6159</v>
+        <v>3.1623</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9111</v>
+        <v>0.9166</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8367</v>
+        <v>0.8461</v>
       </c>
       <c r="D15" t="n">
-        <v>0.961</v>
+        <v>0.867</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9729</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8661</v>
+        <v>0.9724</v>
       </c>
       <c r="G15" t="n">
-        <v>25.5066</v>
+        <v>32.2386</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9046</v>
+        <v>0.952</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8258</v>
+        <v>0.9084</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9319</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.994</v>
+        <v>0.9988</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8788</v>
+        <v>0.9741</v>
       </c>
       <c r="G16" t="n">
-        <v>21.2708</v>
+        <v>3.6056</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9275</v>
+        <v>0.9503</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8647</v>
+        <v>0.9053</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9702</v>
+        <v>0.9548</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9961</v>
+        <v>0.9982</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8884</v>
+        <v>0.9458</v>
       </c>
       <c r="G17" t="n">
-        <v>7.6255</v>
+        <v>2.8284</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9674</v>
+        <v>0.9553</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9369</v>
+        <v>0.9144</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9587</v>
+        <v>0.9228</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9993</v>
+        <v>0.9997</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9762</v>
+        <v>0.9901</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3.1623</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9474</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9001</v>
+        <v>0.9067</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9335</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9529</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6056</v>
+        <v>3.1623</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9262</v>
+        <v>0.9357</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8625</v>
+        <v>0.8791</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9427</v>
+        <v>0.8904</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9821</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9102</v>
+        <v>0.9857</v>
       </c>
       <c r="G20" t="n">
-        <v>25.5019</v>
+        <v>17.3007</v>
       </c>
     </row>
     <row r="21">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9444</v>
+        <v>0.9266</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8632</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9523</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9911</v>
+        <v>0.9901</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9367</v>
+        <v>0.9282</v>
       </c>
       <c r="G21" t="n">
-        <v>18.9842</v>
+        <v>9.9598</v>
       </c>
     </row>
     <row r="22">
@@ -972,22 +972,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7399</v>
+        <v>0.8024</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8089</v>
+        <v>0.7733</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9564</v>
+        <v>0.9822</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6817</v>
+        <v>0.8338</v>
       </c>
       <c r="G22" t="n">
-        <v>53.0429</v>
+        <v>76.4836</v>
       </c>
     </row>
     <row r="23">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9513</v>
+        <v>0.951</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9072</v>
+        <v>0.9066</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9698</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9991</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9335</v>
+        <v>0.9654</v>
       </c>
       <c r="G23" t="n">
         <v>2.2361</v>
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9437</v>
+        <v>0.944</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8934</v>
+        <v>0.8939</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9657</v>
+        <v>0.9631</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9974</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9227</v>
+        <v>0.9255</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
@@ -1047,22 +1047,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9623</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8959</v>
+        <v>0.9274</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9468</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9981</v>
+        <v>0.9991</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9544</v>
+        <v>0.9784</v>
       </c>
       <c r="G25" t="n">
-        <v>4.2426</v>
+        <v>3.1623</v>
       </c>
     </row>
     <row r="26">
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9707</v>
+        <v>0.9605</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9431</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9888</v>
+        <v>0.9421</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9918</v>
+        <v>0.9967</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9533</v>
+        <v>0.9795</v>
       </c>
       <c r="G26" t="n">
-        <v>28.9453</v>
+        <v>11.4018</v>
       </c>
     </row>
     <row r="27">
@@ -1097,22 +1097,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.965</v>
+        <v>0.963</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9323</v>
+        <v>0.9286</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9785</v>
+        <v>0.9498</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9972</v>
+        <v>0.9987</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9518</v>
+        <v>0.9765</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>3.6056</v>
       </c>
     </row>
     <row r="28">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.948</v>
+        <v>0.9425</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9012</v>
+        <v>0.8913</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9483</v>
+        <v>0.9058</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9983</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9478</v>
+        <v>0.9823</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9746</v>
+        <v>5.831</v>
       </c>
     </row>
     <row r="29">
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9344</v>
+        <v>0.9285</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8769</v>
+        <v>0.8666</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9399</v>
+        <v>0.8883</v>
       </c>
       <c r="E29" t="n">
-        <v>0.997</v>
+        <v>0.999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.9726</v>
       </c>
       <c r="G29" t="n">
-        <v>5.6569</v>
+        <v>7.8102</v>
       </c>
     </row>
     <row r="30">
@@ -1172,22 +1172,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9195</v>
+        <v>0.904</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8511</v>
+        <v>0.8247</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9987</v>
+        <v>0.9997</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9223</v>
+        <v>0.9798</v>
       </c>
       <c r="G30" t="n">
-        <v>4.4148</v>
+        <v>5.0099</v>
       </c>
     </row>
     <row r="31">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9196</v>
+        <v>0.8992</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8512</v>
+        <v>0.8169</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9191</v>
+        <v>0.8283</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9969</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9202</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>5.4297</v>
+        <v>23.4599</v>
       </c>
     </row>
     <row r="32">
@@ -1222,22 +1222,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9147</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8429</v>
+        <v>0.8396</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8718</v>
+        <v>0.8472</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9961</v>
+        <v>0.999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9621</v>
+        <v>0.9895</v>
       </c>
       <c r="G32" t="n">
-        <v>28.4059</v>
+        <v>28.8602</v>
       </c>
     </row>
     <row r="33">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9167</v>
+        <v>0.9077</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8462</v>
+        <v>0.831</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8512</v>
+        <v>0.8312</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9932</v>
+        <v>0.9998</v>
       </c>
       <c r="G33" t="n">
-        <v>26.0307</v>
+        <v>18.9737</v>
       </c>
     </row>
     <row r="34">
@@ -1272,22 +1272,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8087</v>
+        <v>0.8186</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6788</v>
+        <v>0.6929</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8848</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9948</v>
+        <v>0.9962</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7096</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0499</v>
+        <v>7.0533</v>
       </c>
     </row>
     <row r="35">
@@ -1297,22 +1297,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9254</v>
+        <v>0.9351</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8612</v>
+        <v>0.878</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9936</v>
+        <v>0.9271</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9973</v>
+        <v>0.999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.866</v>
+        <v>0.9432</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1623</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.858</v>
+        <v>0.9366</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7514</v>
+        <v>0.8807</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9941</v>
+        <v>0.8848</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9364</v>
+        <v>0.9991</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7547</v>
+        <v>0.9947</v>
       </c>
       <c r="G36" t="n">
-        <v>29</v>
+        <v>24.0208</v>
       </c>
     </row>
     <row r="37">
@@ -1347,22 +1347,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9656</v>
+        <v>0.9624</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9336</v>
+        <v>0.9275</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9684</v>
+        <v>0.9396</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9971</v>
+        <v>0.999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9629</v>
+        <v>0.9862</v>
       </c>
       <c r="G37" t="n">
-        <v>16</v>
+        <v>6.0828</v>
       </c>
     </row>
     <row r="38">
@@ -1372,22 +1372,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9515</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9075</v>
+        <v>0.9327</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9252</v>
+        <v>0.9348</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9794</v>
+        <v>0.9976</v>
       </c>
       <c r="G38" t="n">
-        <v>8</v>
+        <v>3.1623</v>
       </c>
     </row>
     <row r="39">
@@ -1397,22 +1397,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9641</v>
+        <v>0.9676</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9307</v>
+        <v>0.9372</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9454</v>
+        <v>0.9581</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9976</v>
+        <v>0.9967</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9836</v>
+        <v>0.9772</v>
       </c>
       <c r="G39" t="n">
-        <v>28.7082</v>
+        <v>5.831</v>
       </c>
     </row>
     <row r="40">
@@ -1422,22 +1422,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8464</v>
+        <v>0.8562</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7337</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8283</v>
+        <v>0.8456</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9968</v>
+        <v>0.9967</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8653</v>
+        <v>0.867</v>
       </c>
       <c r="G40" t="n">
-        <v>9.2195</v>
+        <v>64.846</v>
       </c>
     </row>
     <row r="41">
@@ -1447,22 +1447,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8527</v>
+        <v>0.9433</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7432</v>
+        <v>0.8928</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9655</v>
+        <v>0.9036</v>
       </c>
       <c r="E41" t="n">
-        <v>0.983</v>
+        <v>0.9993</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7635</v>
+        <v>0.9868</v>
       </c>
       <c r="G41" t="n">
-        <v>32.36</v>
+        <v>12.9216</v>
       </c>
     </row>
     <row r="42">
@@ -1472,22 +1472,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9379</v>
+        <v>0.884</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8831</v>
+        <v>0.7921</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9563</v>
+        <v>0.9355</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9981</v>
+        <v>0.9959</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9202</v>
+        <v>0.8379</v>
       </c>
       <c r="G42" t="n">
-        <v>5.3852</v>
+        <v>11.1803</v>
       </c>
     </row>
     <row r="43">
@@ -1497,19 +1497,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9758</v>
+        <v>0.9741</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9528</v>
+        <v>0.9495</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9754</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9694</v>
+        <v>0.9727</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -1522,22 +1522,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9375</v>
+        <v>0.866</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8824</v>
+        <v>0.7637</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9389</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9362</v>
+        <v>0.9737</v>
       </c>
       <c r="G44" t="n">
-        <v>10.4403</v>
+        <v>64.53279999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1547,22 +1547,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9338</v>
+        <v>0.8999</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8758</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8778</v>
+        <v>0.8182</v>
       </c>
       <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.9997</v>
       </c>
-      <c r="F45" t="n">
-        <v>0.9974</v>
-      </c>
       <c r="G45" t="n">
-        <v>26.9016</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9411</v>
+        <v>0.9332</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8887</v>
+        <v>0.8748</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8912</v>
+        <v>0.875</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9968</v>
+        <v>0.9998</v>
       </c>
       <c r="G46" t="n">
-        <v>19.0171</v>
+        <v>11.8804</v>
       </c>
     </row>
     <row r="47">
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9498</v>
+        <v>0.9377</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9044</v>
+        <v>0.8827</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.8833</v>
       </c>
       <c r="E47" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9946</v>
+        <v>0.9992</v>
       </c>
       <c r="G47" t="n">
-        <v>35.6405</v>
+        <v>17.1114</v>
       </c>
     </row>
     <row r="48">
@@ -1622,22 +1622,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9782</v>
+        <v>0.9579</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9573</v>
+        <v>0.9193</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9851</v>
+        <v>0.9235</v>
       </c>
       <c r="E48" t="n">
-        <v>0.994</v>
+        <v>0.9991</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9714</v>
+        <v>0.995</v>
       </c>
       <c r="G48" t="n">
-        <v>29</v>
+        <v>20.1367</v>
       </c>
     </row>
     <row r="49">
@@ -1647,22 +1647,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9658</v>
+        <v>0.9768</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9338</v>
+        <v>0.9547</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9825</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9903</v>
+        <v>0.9954</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9423</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>28.1137</v>
+        <v>3.0243</v>
       </c>
     </row>
     <row r="50">
@@ -1672,22 +1672,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9512</v>
+        <v>0.9611</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9069</v>
+        <v>0.925</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9821</v>
+        <v>0.9607</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9937</v>
+        <v>0.9971</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9222</v>
+        <v>0.9614</v>
       </c>
       <c r="G50" t="n">
-        <v>22.8696</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -1697,22 +1697,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9449</v>
+        <v>0.9448</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8955</v>
+        <v>0.8954</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9846</v>
+        <v>0.9687</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9913</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9082</v>
+        <v>0.9221</v>
       </c>
       <c r="G51" t="n">
-        <v>35.1244</v>
+        <v>9.969799999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1722,22 +1722,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9437</v>
+        <v>0.9389</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8934</v>
+        <v>0.8848</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9982</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9734</v>
+        <v>0.9769</v>
       </c>
       <c r="G52" t="n">
-        <v>9.0083</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -1747,22 +1747,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9281</v>
+        <v>0.9536</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8659</v>
+        <v>0.9112</v>
       </c>
       <c r="D53" t="n">
-        <v>0.988</v>
+        <v>0.9667</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9941</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8751</v>
+        <v>0.9407</v>
       </c>
       <c r="G53" t="n">
-        <v>15.7472</v>
+        <v>4.4721</v>
       </c>
     </row>
     <row r="54">
@@ -1772,22 +1772,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9045</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8256</v>
+        <v>0.4713</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8767</v>
+        <v>0.477</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9973</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9341</v>
+        <v>0.975</v>
       </c>
       <c r="G54" t="n">
-        <v>14.8582</v>
+        <v>47.4974</v>
       </c>
     </row>
     <row r="55">
@@ -1797,22 +1797,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.881</v>
+        <v>0.8834</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7872</v>
+        <v>0.7912</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8509</v>
+        <v>0.8101</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9132</v>
+        <v>0.9714</v>
       </c>
       <c r="G55" t="n">
-        <v>70.6416</v>
+        <v>4.4721</v>
       </c>
     </row>
     <row r="56">
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9095</v>
+        <v>0.891</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8341</v>
+        <v>0.8034</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9407</v>
+        <v>0.8045</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8803</v>
+        <v>0.9983</v>
       </c>
       <c r="G56" t="n">
-        <v>9.0932</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -1847,22 +1847,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8744</v>
+        <v>0.9035</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7768</v>
+        <v>0.8239</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9836</v>
+        <v>0.8656</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9952</v>
+        <v>0.9991</v>
       </c>
       <c r="F57" t="n">
-        <v>0.787</v>
+        <v>0.9448</v>
       </c>
       <c r="G57" t="n">
-        <v>12.2218</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1872,22 +1872,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9527</v>
+        <v>0.8668</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9097</v>
+        <v>0.7649</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.9547</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9981</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9554</v>
+        <v>0.7937</v>
       </c>
       <c r="G58" t="n">
-        <v>3.6056</v>
+        <v>17.6932</v>
       </c>
     </row>
     <row r="59">
@@ -1897,22 +1897,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8951</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8101</v>
+        <v>0.7849</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9852</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9911</v>
+        <v>0.9907</v>
       </c>
       <c r="F59" t="n">
-        <v>0.82</v>
+        <v>0.8106</v>
       </c>
       <c r="G59" t="n">
-        <v>15.7876</v>
+        <v>20.8655</v>
       </c>
     </row>
     <row r="60">
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8838</v>
+        <v>0.8459</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7917</v>
+        <v>0.733</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9809</v>
+        <v>0.7423</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9937</v>
+        <v>0.9997</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8041</v>
+        <v>0.9831</v>
       </c>
       <c r="G60" t="n">
-        <v>9</v>
+        <v>15.975</v>
       </c>
     </row>
     <row r="61">
@@ -1947,22 +1947,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.923</v>
+        <v>0.9256</v>
       </c>
       <c r="C61" t="n">
-        <v>0.857</v>
+        <v>0.8615</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8983</v>
+        <v>0.8778</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9994</v>
+        <v>0.9998</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9492</v>
+        <v>0.9789</v>
       </c>
       <c r="G61" t="n">
-        <v>4.1231</v>
+        <v>3.6056</v>
       </c>
     </row>
     <row r="62">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9756</v>
+        <v>0.9448</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9524</v>
+        <v>0.8954</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9826</v>
+        <v>0.9028</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9907</v>
+        <v>0.9976</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9687</v>
+        <v>0.991</v>
       </c>
       <c r="G62" t="n">
-        <v>14.5119</v>
+        <v>26.2068</v>
       </c>
     </row>
     <row r="63">
@@ -1997,22 +1997,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9781</v>
+        <v>0.9696</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9571</v>
+        <v>0.9411</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9688</v>
+        <v>0.9537</v>
       </c>
       <c r="E63" t="n">
         <v>0.9994</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9876</v>
+        <v>0.9861</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="64">
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9299741935483871</v>
+        <v>0.9262983870967743</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8724951612903225</v>
+        <v>0.8667774193548387</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9424032258064515</v>
+        <v>0.8993693548387098</v>
       </c>
       <c r="E64" t="n">
-        <v>0.994083870967742</v>
+        <v>0.9977709677419355</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9223112903225805</v>
+        <v>0.9609806451612903</v>
       </c>
       <c r="G64" t="n">
-        <v>15.06378548387097</v>
+        <v>12.59552741935484</v>
       </c>
     </row>
   </sheetData>
